--- a/Result/profitability/1476.xlsx
+++ b/Result/profitability/1476.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>4.936249999999999</v>
+        <v>4.835</v>
       </c>
       <c r="N2" t="n">
-        <v>28.4475</v>
+        <v>28.15875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1275</v>
+        <v>4.0575</v>
       </c>
       <c r="N3" t="n">
-        <v>26.51625</v>
+        <v>26.53625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.42375</v>
+        <v>3.36625</v>
       </c>
       <c r="N4" t="n">
-        <v>25.2025</v>
+        <v>25.17875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>2.71125</v>
+        <v>3.145</v>
       </c>
       <c r="N5" t="n">
-        <v>23.9525</v>
+        <v>24.4975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.50875</v>
+        <v>2.46375</v>
       </c>
       <c r="N6" t="n">
-        <v>23.8075</v>
+        <v>23.97625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8275</v>
+        <v>1.81375</v>
       </c>
       <c r="N7" t="n">
-        <v>23.62375</v>
+        <v>23.60125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1775</v>
+        <v>1.04875</v>
       </c>
       <c r="N8" t="n">
-        <v>22.795</v>
+        <v>22.525</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10086</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7059</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3027</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1935</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.18%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>74</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2009</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1553</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5.642499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.88125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1539611360239164</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0671433012123096</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.584474885844749</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.360000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1699805068226121</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
